--- a/sheets/조재수대금교본/검수/꽃분네야.xlsx
+++ b/sheets/조재수대금교본/검수/꽃분네야.xlsx
@@ -3191,7 +3191,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3245,7 +3245,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3265,17 +3265,9 @@
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="86.26" customHeight="true">
@@ -3294,8 +3286,7 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ﾉ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -3316,7 +3307,7 @@
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -3326,11 +3317,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -3338,23 +3325,15 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="86.26" customHeight="true">
@@ -3367,11 +3346,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21"/>
       <c r="I7" s="23"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J7" s="21"/>
       <c r="K7" s="23"/>
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
@@ -3384,30 +3359,20 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∼
-‹</t>
+          <t xml:space="preserve">㴌∼</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㄴ
-淋
-‹</t>
+          <t xml:space="preserve">淋
+淋</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
@@ -3416,24 +3381,18 @@
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰潢
-‹</t>
+汰潢</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -3491,19 +3450,11 @@
     </row>
     <row r="10" ht="86.26" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="23"/>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -3511,87 +3462,63 @@
         </is>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="23"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="86.26" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳⌝
-湳
-‹</t>
+          <t xml:space="preserve">湳
+湳</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -3687,43 +3614,22 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="24"/>

--- a/sheets/조재수대금교본/검수/꽃분네야.xlsx
+++ b/sheets/조재수대금교본/검수/꽃분네야.xlsx
@@ -3191,7 +3191,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3245,7 +3245,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3265,9 +3265,17 @@
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="86.26" customHeight="true">
@@ -3286,7 +3294,8 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ﾉ</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -3307,7 +3316,7 @@
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∼</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -3317,7 +3326,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -3325,15 +3338,23 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="86.26" customHeight="true">
@@ -3367,7 +3388,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋ㄴ
 淋</t>
         </is>
       </c>
@@ -3450,11 +3471,19 @@
     </row>
     <row r="10" ht="86.26" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
-      <c r="F10" s="21"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -3462,57 +3491,79 @@
         </is>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M10" s="23"/>
-      <c r="N10" s="21"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="86.26" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳⌝
 湳</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="O11" s="24"/>

--- a/sheets/조재수대금교본/검수/꽃분네야.xlsx
+++ b/sheets/조재수대금교본/검수/꽃분네야.xlsx
@@ -3143,28 +3143,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -3376,7 +3376,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3656,7 +3656,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3691,6 +3691,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>